--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A8899629-76ED-4EC4-933A-8F9C7D00A53F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{FFDF7B8A-0406-4FAF-946E-CE2267030FB4}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="73">
   <si>
     <t>Result</t>
   </si>
@@ -234,13 +234,28 @@
     <t>Thu May 21 20:01:21 IST 2026</t>
   </si>
   <si>
+    <t>Thu May 21 20:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 20:06:34 IST 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Thu May 21 20:05:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 20:06:34 IST 2026</t>
+    <t>Tue Jun 02 21:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 21:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 21:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 03 17:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 03 17:07:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -860,13 +875,16 @@
     </row>
     <row ht="37.5" r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>6</v>
@@ -898,13 +916,16 @@
     </row>
     <row ht="37.5" r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>6</v>
@@ -939,7 +960,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -980,7 +1001,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
@@ -1161,10 +1182,10 @@
     </row>
     <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1211,7 +1232,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>33</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="96">
   <si>
     <t>Result</t>
   </si>
@@ -256,6 +256,75 @@
   </si>
   <si>
     <t>Wed Jun 03 17:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:11:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:12:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:13:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:15:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:16:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:17:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:20:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:22:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:23:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:24:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 19:25:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:04:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:05:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:07:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:09:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:10:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:10:53 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -878,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -919,7 +988,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>36</v>
@@ -960,7 +1029,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -1001,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
@@ -1182,10 +1251,10 @@
     </row>
     <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1232,7 +1301,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>33</v>
@@ -1303,7 +1372,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>34</v>
@@ -1344,7 +1413,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>35</v>
@@ -1386,7 +1455,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>49</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="110">
   <si>
     <t>Result</t>
   </si>
@@ -325,6 +325,48 @@
   </si>
   <si>
     <t>Thu Jun 18 04:10:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:01:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:02:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:03:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:04:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:07:46 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -824,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
@@ -943,11 +985,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
-        <v>87</v>
+      <c r="B2" t="s" s="1">
+        <v>96</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -984,11 +1026,11 @@
       </c>
     </row>
     <row ht="37.5" r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
-        <v>88</v>
+      <c r="B3" t="s" s="1">
+        <v>97</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>36</v>
@@ -1025,11 +1067,11 @@
       </c>
     </row>
     <row ht="62.5" r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
-        <v>89</v>
+      <c r="B4" t="s" s="1">
+        <v>98</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -1066,11 +1108,11 @@
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="B5" t="s">
-        <v>90</v>
+      <c r="B5" t="s" s="1">
+        <v>99</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
@@ -1120,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
@@ -1250,11 +1292,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
-        <v>91</v>
+      <c r="B2" t="s" s="6">
+        <v>105</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1297,11 +1339,11 @@
       </c>
     </row>
     <row ht="37.5" r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B3" t="s">
-        <v>92</v>
+      <c r="B3" t="s" s="6">
+        <v>106</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>33</v>
@@ -1368,11 +1410,11 @@
       </c>
     </row>
     <row ht="37.5" r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
-        <v>93</v>
+      <c r="B4" t="s" s="6">
+        <v>107</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>34</v>
@@ -1409,11 +1451,11 @@
       </c>
     </row>
     <row customHeight="1" ht="42" r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B5" t="s">
-        <v>94</v>
+      <c r="B5" t="s" s="6">
+        <v>108</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>35</v>
@@ -1451,11 +1493,11 @@
       </c>
     </row>
     <row ht="50" r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B6" t="s">
-        <v>95</v>
+      <c r="B6" t="s" s="6">
+        <v>109</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>49</v>
